--- a/SGC-CKN/Excel/39cf284b-b4c1-476f-8f88-461ded65f753_Lô_CT-02_P1_D800_01-04-2026.xlsx
+++ b/SGC-CKN/Excel/39cf284b-b4c1-476f-8f88-461ded65f753_Lô_CT-02_P1_D800_01-04-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>P1</t>
+    <t>P1-50</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>

--- a/SGC-CKN/Excel/39cf284b-b4c1-476f-8f88-461ded65f753_Lô_CT-02_P1_D800_01-04-2026.xlsx
+++ b/SGC-CKN/Excel/39cf284b-b4c1-476f-8f88-461ded65f753_Lô_CT-02_P1_D800_01-04-2026.xlsx
@@ -222,7 +222,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -253,18 +253,12 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFC2410C"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
       <color rgb="FF78350F"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color rgb="FFC2410C"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
@@ -340,7 +334,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC2626"/>
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -511,70 +505,70 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1160,7 +1154,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-1.22</v>
@@ -1169,10 +1163,10 @@
         <v>0.52</v>
       </c>
       <c r="I11" s="5">
-        <v>0.51</v>
+        <v>1.22</v>
       </c>
       <c r="J11" s="8">
-        <v>0.99</v>
+        <v>2.36</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1268,16 +1262,16 @@
         <v>-7.62</v>
       </c>
       <c r="G14" s="16">
-        <v>-16.92</v>
+        <v>-16.42</v>
       </c>
       <c r="H14" s="16">
         <v>0.8</v>
       </c>
       <c r="I14" s="16">
-        <v>9.3</v>
+        <v>8.8</v>
       </c>
       <c r="J14" s="12">
-        <v>11.63</v>
+        <v>11</v>
       </c>
       <c r="K14" s="17" t="s">
         <v>34</v>
@@ -1300,7 +1294,7 @@
         <v>43</v>
       </c>
       <c r="F15" s="19">
-        <v>-16.92</v>
+        <v>-16.42</v>
       </c>
       <c r="G15" s="19">
         <v>-21.62</v>
@@ -1309,10 +1303,10 @@
         <v>0.55</v>
       </c>
       <c r="I15" s="19">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="J15" s="12">
-        <v>8.55</v>
+        <v>9.45</v>
       </c>
       <c r="K15" s="20" t="s">
         <v>34</v>
@@ -1373,16 +1367,16 @@
         <v>-25.62</v>
       </c>
       <c r="G17" s="25">
-        <v>-35.89</v>
+        <v>-39.01</v>
       </c>
       <c r="H17" s="25">
         <v>1.12</v>
       </c>
       <c r="I17" s="25">
-        <v>10.27</v>
+        <v>13.39</v>
       </c>
       <c r="J17" s="12">
-        <v>9.2</v>
+        <v>11.99</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>50</v>
@@ -1405,7 +1399,7 @@
         <v>53</v>
       </c>
       <c r="F18" s="28">
-        <v>-35.89</v>
+        <v>-39.01</v>
       </c>
       <c r="G18" s="28">
         <v>-44.42</v>
@@ -1414,10 +1408,10 @@
         <v>1.45</v>
       </c>
       <c r="I18" s="28">
-        <v>8.53</v>
-      </c>
-      <c r="J18" s="12">
-        <v>5.88</v>
+        <v>5.41</v>
+      </c>
+      <c r="J18" s="8">
+        <v>3.73</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>54</v>
@@ -1572,7 +1566,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-1.22</v>
@@ -1581,10 +1575,10 @@
         <v>0.52</v>
       </c>
       <c r="H2" s="5">
-        <v>0.51</v>
+        <v>1.22</v>
       </c>
       <c r="I2" s="8">
-        <v>0.99</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1662,16 +1656,16 @@
         <v>-7.62</v>
       </c>
       <c r="F5" s="16">
-        <v>-16.92</v>
+        <v>-16.42</v>
       </c>
       <c r="G5" s="16">
         <v>0.8</v>
       </c>
       <c r="H5" s="16">
-        <v>9.3</v>
+        <v>8.8</v>
       </c>
       <c r="I5" s="12">
-        <v>11.63</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1688,7 +1682,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="19">
-        <v>-16.92</v>
+        <v>-16.42</v>
       </c>
       <c r="F6" s="19">
         <v>-21.62</v>
@@ -1697,10 +1691,10 @@
         <v>0.55</v>
       </c>
       <c r="H6" s="19">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="I6" s="12">
-        <v>8.55</v>
+        <v>9.45</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1749,16 +1743,16 @@
         <v>-25.62</v>
       </c>
       <c r="F8" s="25">
-        <v>-35.89</v>
+        <v>-39.01</v>
       </c>
       <c r="G8" s="25">
         <v>1.12</v>
       </c>
       <c r="H8" s="25">
-        <v>10.27</v>
+        <v>13.39</v>
       </c>
       <c r="I8" s="12">
-        <v>9.2</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1775,7 +1769,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>-35.89</v>
+        <v>-39.01</v>
       </c>
       <c r="F9" s="28">
         <v>-44.42</v>
@@ -1784,10 +1778,10 @@
         <v>1.45</v>
       </c>
       <c r="H9" s="28">
-        <v>8.53</v>
-      </c>
-      <c r="I9" s="12">
-        <v>5.88</v>
+        <v>5.41</v>
+      </c>
+      <c r="I9" s="8">
+        <v>3.73</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1804,7 +1798,7 @@
         <v>8</v>
       </c>
       <c r="E10" s="33">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="F10" s="33">
         <v>-44.42</v>
@@ -1813,10 +1807,10 @@
         <v>5.7</v>
       </c>
       <c r="H10" s="33">
-        <v>43.71</v>
+        <v>44.42</v>
       </c>
       <c r="I10" s="33">
-        <v>7.67</v>
+        <v>7.79</v>
       </c>
     </row>
   </sheetData>
